--- a/artfynd/A 57076-2020 artfynd.xlsx
+++ b/artfynd/A 57076-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 57076-2020 artfynd.xlsx
+++ b/artfynd/A 57076-2020 artfynd.xlsx
@@ -805,10 +805,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>98321206</v>
+        <v>75284504</v>
       </c>
       <c r="B3" t="n">
-        <v>98534</v>
+        <v>100421</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -840,7 +840,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -853,14 +853,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Blomsternipan, Ång</t>
+          <t>Näsåker P, Blomsternipan, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>595189.8407022246</v>
+        <v>595190</v>
       </c>
       <c r="R3" t="n">
-        <v>7035588.39521525</v>
+        <v>7035588</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -885,29 +885,29 @@
           <t>Ådals-Liden</t>
         </is>
       </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Y-Sol-0099-biogeo</t>
+        </is>
+      </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2021-06-04</t>
+          <t>2009-07-25</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2021-06-04</t>
+          <t>2009-07-25</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>2 sterila plantor</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -923,7 +923,7 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kerstin Wörler</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
@@ -933,13 +933,13 @@
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>Nipsippa Y-län</t>
+          <t>Floraväkteri Sverige</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>110211842</v>
+        <v>98321206</v>
       </c>
       <c r="B4" t="n">
         <v>98534</v>
@@ -977,19 +977,27 @@
           <t>2</t>
         </is>
       </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Söder om Näsåker, nära älven., Ång</t>
+          <t>Blomsternipan, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>595191.8996489941</v>
+        <v>595189.8407022246</v>
       </c>
       <c r="R4" t="n">
-        <v>7035579.499253293</v>
+        <v>7035588.39521525</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1013,7 +1021,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-06-13</t>
+          <t>2021-06-04</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1023,7 +1031,7 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-06-13</t>
+          <t>2021-06-04</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1033,7 +1041,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>I sydvänd slänt på sandig, brant åskam.</t>
+          <t>2 sterila plantor</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1042,28 +1050,33 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Kerstin Wörler</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Nipsippa Y-län</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>110211841</v>
+        <v>110211842</v>
       </c>
       <c r="B5" t="n">
-        <v>89673</v>
+        <v>98534</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1076,34 +1089,38 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>658</v>
+        <v>1332</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Nipsippa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Pulsatilla patens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) Mill.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Söder om Näsåker, nära älven., Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>595249.2583857939</v>
+        <v>595191.8996489941</v>
       </c>
       <c r="R5" t="n">
-        <v>7035565.981385023</v>
+        <v>7035579.499253293</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1148,6 +1165,11 @@
           <t>00:00</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>I sydvänd slänt på sandig, brant åskam.</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1156,11 +1178,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Murken granlåga med lite bark kvar.</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1177,10 +1194,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>110212368</v>
+        <v>110211841</v>
       </c>
       <c r="B6" t="n">
-        <v>56521</v>
+        <v>89673</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1193,38 +1210,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103035</v>
+        <v>658</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kråka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Corvus corone</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Söder om Näsåker, nära älven., Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>595168.828604917</v>
+        <v>595249.2583857939</v>
       </c>
       <c r="R6" t="n">
-        <v>7035525.963256468</v>
+        <v>7035565.981385023</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1277,6 +1290,11 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Murken granlåga med lite bark kvar.</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1293,10 +1311,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>111638335</v>
+        <v>110212368</v>
       </c>
       <c r="B7" t="n">
-        <v>95532</v>
+        <v>56521</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1305,38 +1323,42 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>103035</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Corvus corone</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Söder om Näsåker, nära älven., Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>595260</v>
+        <v>595168.828604917</v>
       </c>
       <c r="R7" t="n">
-        <v>7035583</v>
+        <v>7035525.963256468</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1366,14 +1388,19 @@
           <t>2022-06-13</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2022-06-13</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Stort bestånd.</t>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1388,22 +1415,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Alexandra Holmgren</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Alexandra Holmgren</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>111638343</v>
+        <v>111638335</v>
       </c>
       <c r="B8" t="n">
-        <v>95723</v>
+        <v>95532</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1416,38 +1443,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220250</v>
+        <v>221945</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Strutbräken</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Matteuccia struthiopteris</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Tod.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Söder om Näsåker, nära älven., Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>595350</v>
+        <v>595260</v>
       </c>
       <c r="R8" t="n">
-        <v>7035563</v>
+        <v>7035583</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1484,7 +1507,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>I örtrik brant.</t>
+          <t>Stort bestånd.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1511,7 +1534,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>111638342</v>
+        <v>111638343</v>
       </c>
       <c r="B9" t="n">
         <v>95723</v>
@@ -1546,7 +1569,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1555,10 +1578,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>595216</v>
+        <v>595350</v>
       </c>
       <c r="R9" t="n">
-        <v>7035642</v>
+        <v>7035563</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1595,7 +1618,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Långt ner i branten, nedanför lövskogen.</t>
+          <t>I örtrik brant.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1622,10 +1645,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>112995787</v>
+        <v>111638342</v>
       </c>
       <c r="B10" t="n">
-        <v>99568</v>
+        <v>95723</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1634,57 +1657,45 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1332</v>
+        <v>220250</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Nipsippa</t>
+          <t>Strutbräken</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pulsatilla patens</t>
+          <t>Matteuccia struthiopteris</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>(L.) Tod.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Blomsternipan, Ång</t>
+          <t>Söder om Näsåker, nära älven., Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>595190</v>
+        <v>595216</v>
       </c>
       <c r="R10" t="n">
-        <v>7035588</v>
+        <v>7035642</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1708,17 +1719,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2023-06-04</t>
+          <t>2022-06-13</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2023-06-04</t>
+          <t>2022-06-13</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Två sterila plantor.</t>
+          <t>Långt ner i branten, nedanför lövskogen.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1727,26 +1738,21 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Alexandra Holmgren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>Nipsippa Y-län</t>
-        </is>
-      </c>
+          <t>Alexandra Holmgren</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">

--- a/artfynd/A 57076-2020 artfynd.xlsx
+++ b/artfynd/A 57076-2020 artfynd.xlsx
@@ -808,7 +808,7 @@
         <v>75284504</v>
       </c>
       <c r="B3" t="n">
-        <v>100421</v>
+        <v>100430</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 57076-2020 artfynd.xlsx
+++ b/artfynd/A 57076-2020 artfynd.xlsx
@@ -808,7 +808,7 @@
         <v>75284504</v>
       </c>
       <c r="B3" t="n">
-        <v>100430</v>
+        <v>100438</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 57076-2020 artfynd.xlsx
+++ b/artfynd/A 57076-2020 artfynd.xlsx
@@ -808,7 +808,7 @@
         <v>75284504</v>
       </c>
       <c r="B3" t="n">
-        <v>100438</v>
+        <v>100440</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 57076-2020 artfynd.xlsx
+++ b/artfynd/A 57076-2020 artfynd.xlsx
@@ -808,7 +808,7 @@
         <v>75284504</v>
       </c>
       <c r="B3" t="n">
-        <v>100456</v>
+        <v>100466</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 57076-2020 artfynd.xlsx
+++ b/artfynd/A 57076-2020 artfynd.xlsx
@@ -678,11 +678,11 @@
         <v>378900</v>
       </c>
       <c r="B2" t="n">
-        <v>98534</v>
+        <v>100466</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>595189.8673680641</v>
+        <v>595190</v>
       </c>
       <c r="R2" t="n">
-        <v>7035587.500279763</v>
+        <v>7035588</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -762,19 +762,9 @@
           <t>2012-05-25</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2012-05-25</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -805,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>75284504</v>
+        <v>66233725</v>
       </c>
       <c r="B3" t="n">
-        <v>100466</v>
+        <v>98534</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -840,7 +830,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -848,19 +838,22 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Näsåker P, Blomsternipan, Ång</t>
+          <t>Näsåker, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>595190</v>
+        <v>595189.8673680641</v>
       </c>
       <c r="R3" t="n">
-        <v>7035588</v>
+        <v>7035587.500279763</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -885,29 +878,24 @@
           <t>Ådals-Liden</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>Y-Sol-0099-biogeo</t>
-        </is>
-      </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2009-07-25</t>
+          <t>2017-06-07</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2009-07-25</t>
+          <t>2017-06-07</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -916,26 +904,21 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Marcus Vestlund</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+          <t>Marcus Vestlund, Ola Borin, Bo Karlsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">

--- a/artfynd/A 57076-2020 artfynd.xlsx
+++ b/artfynd/A 57076-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>378900</v>
       </c>
       <c r="B2" t="n">
-        <v>100466</v>
+        <v>100478</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 57076-2020 artfynd.xlsx
+++ b/artfynd/A 57076-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>378900</v>
       </c>
       <c r="B2" t="n">
-        <v>100478</v>
+        <v>100483</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 57076-2020 artfynd.xlsx
+++ b/artfynd/A 57076-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>378900</v>
       </c>
       <c r="B2" t="n">
-        <v>100483</v>
+        <v>100492</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -692,11 +692,6 @@
       </c>
       <c r="E2" t="n">
         <v>1332</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Nipsippa</t>
-        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>

--- a/artfynd/A 57076-2020 artfynd.xlsx
+++ b/artfynd/A 57076-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>378900</v>
       </c>
       <c r="B2" t="n">
-        <v>100492</v>
+        <v>100505</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -692,6 +692,11 @@
       </c>
       <c r="E2" t="n">
         <v>1332</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Nipsippa</t>
+        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>

--- a/artfynd/A 57076-2020 artfynd.xlsx
+++ b/artfynd/A 57076-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>378900</v>
       </c>
       <c r="B2" t="n">
-        <v>100505</v>
+        <v>100518</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 57076-2020 artfynd.xlsx
+++ b/artfynd/A 57076-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>378900</v>
       </c>
       <c r="B2" t="n">
-        <v>100518</v>
+        <v>100521</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 57076-2020 artfynd.xlsx
+++ b/artfynd/A 57076-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>378900</v>
       </c>
       <c r="B2" t="n">
-        <v>100521</v>
+        <v>100522</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 57076-2020 artfynd.xlsx
+++ b/artfynd/A 57076-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>378900</v>
       </c>
       <c r="B2" t="n">
-        <v>100522</v>
+        <v>100525</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 57076-2020 artfynd.xlsx
+++ b/artfynd/A 57076-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>378900</v>
       </c>
       <c r="B2" t="n">
-        <v>100628</v>
+        <v>100636</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 57076-2020 artfynd.xlsx
+++ b/artfynd/A 57076-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -795,7 +795,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>66233725</v>
+        <v>110211842</v>
       </c>
       <c r="B3" t="n">
         <v>98534</v>
@@ -833,30 +833,19 @@
           <t>2</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Näsåker, Ång</t>
+          <t>Söder om Näsåker, nära älven., Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>595189.8673680641</v>
+        <v>595191.8996489941</v>
       </c>
       <c r="R3" t="n">
-        <v>7035587.500279763</v>
+        <v>7035579.499253293</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -880,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2017-06-07</t>
+          <t>2022-06-13</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -890,12 +879,17 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2017-06-07</t>
+          <t>2022-06-13</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
           <t>00:00</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>I sydvänd slänt på sandig, brant åskam.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -910,22 +904,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Marcus Vestlund</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Marcus Vestlund, Ola Borin, Bo Karlsson</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>98321206</v>
+        <v>110211841</v>
       </c>
       <c r="B4" t="n">
-        <v>98534</v>
+        <v>89673</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -938,49 +932,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1332</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Nipsippa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pulsatilla patens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Blomsternipan, Ång</t>
+          <t>Söder om Näsåker, nära älven., Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>595189.8407022246</v>
+        <v>595249.2583857939</v>
       </c>
       <c r="R4" t="n">
-        <v>7035588.39521525</v>
+        <v>7035565.981385023</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1004,7 +986,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2021-06-04</t>
+          <t>2022-06-13</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1014,7 +996,7 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2021-06-04</t>
+          <t>2022-06-13</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1022,44 +1004,39 @@
           <t>00:00</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>2 sterila plantor</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Murken granlåga med lite bark kvar.</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kerstin Wörler</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>Nipsippa Y-län</t>
-        </is>
-      </c>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>110211842</v>
+        <v>110212368</v>
       </c>
       <c r="B5" t="n">
-        <v>98534</v>
+        <v>56521</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1072,26 +1049,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1332</v>
+        <v>103035</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nipsippa</t>
+          <t>Kråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pulsatilla patens</t>
+          <t>Corvus corone</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1100,10 +1077,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>595191.8996489941</v>
+        <v>595168.828604917</v>
       </c>
       <c r="R5" t="n">
-        <v>7035579.499253293</v>
+        <v>7035525.963256468</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1146,11 +1123,6 @@
       <c r="AB5" t="inlineStr">
         <is>
           <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>I sydvänd slänt på sandig, brant åskam.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1177,10 +1149,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>110211841</v>
+        <v>111638335</v>
       </c>
       <c r="B6" t="n">
-        <v>89673</v>
+        <v>95532</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1189,25 +1161,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>658</v>
+        <v>221945</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1217,10 +1189,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>595249.2583857939</v>
+        <v>595260</v>
       </c>
       <c r="R6" t="n">
-        <v>7035565.981385023</v>
+        <v>7035583</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1250,19 +1222,14 @@
           <t>2022-06-13</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2022-06-13</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Stort bestånd.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1273,31 +1240,26 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Murken granlåga med lite bark kvar.</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Alexandra Holmgren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Alexandra Holmgren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>110212368</v>
+        <v>111638343</v>
       </c>
       <c r="B7" t="n">
-        <v>56521</v>
+        <v>95723</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1306,30 +1268,30 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103035</v>
+        <v>220250</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kråka</t>
+          <t>Strutbräken</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Corvus corone</t>
+          <t>Matteuccia struthiopteris</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Tod.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1338,10 +1300,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>595168.828604917</v>
+        <v>595350</v>
       </c>
       <c r="R7" t="n">
-        <v>7035525.963256468</v>
+        <v>7035563</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1371,19 +1333,14 @@
           <t>2022-06-13</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2022-06-13</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>I örtrik brant.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1398,22 +1355,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Alexandra Holmgren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Alexandra Holmgren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>111638335</v>
+        <v>111638342</v>
       </c>
       <c r="B8" t="n">
-        <v>95532</v>
+        <v>95723</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1426,34 +1383,38 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221945</v>
+        <v>220250</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Strutbräken</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Matteuccia struthiopteris</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) Tod.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Söder om Näsåker, nära älven., Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>595260</v>
+        <v>595216</v>
       </c>
       <c r="R8" t="n">
-        <v>7035583</v>
+        <v>7035642</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1490,7 +1451,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Stort bestånd.</t>
+          <t>Långt ner i branten, nedanför lövskogen.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1517,10 +1478,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>111638343</v>
+        <v>118202633</v>
       </c>
       <c r="B9" t="n">
-        <v>95723</v>
+        <v>100122</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1529,45 +1490,45 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220250</v>
+        <v>1332</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Strutbräken</t>
+          <t>Nipsippa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Matteuccia struthiopteris</t>
+          <t>Pulsatilla patens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Tod.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>(L.) Mill.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Söder om Näsåker, nära älven., Ång</t>
+          <t>Näsåkers nipa, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>595350</v>
+        <v>595183</v>
       </c>
       <c r="R9" t="n">
-        <v>7035563</v>
+        <v>7035590</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1591,17 +1552,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2022-06-13</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2022-06-13</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>I örtrik brant.</t>
+          <t>2 plantor</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1610,244 +1571,22 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Alexandra Holmgren</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Alexandra Holmgren</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>111638342</v>
-      </c>
-      <c r="B10" t="n">
-        <v>95723</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>220250</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Strutbräken</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Matteuccia struthiopteris</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>(L.) Tod.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>Söder om Näsåker, nära älven., Ång</t>
-        </is>
-      </c>
-      <c r="Q10" t="n">
-        <v>595216</v>
-      </c>
-      <c r="R10" t="n">
-        <v>7035642</v>
-      </c>
-      <c r="S10" t="n">
-        <v>5</v>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>Sollefteå</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>Ådals-Liden</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>2022-06-13</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>2022-06-13</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Långt ner i branten, nedanför lövskogen.</t>
-        </is>
-      </c>
-      <c r="AD10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT10" t="inlineStr"/>
-      <c r="AW10" t="inlineStr">
-        <is>
-          <t>Alexandra Holmgren</t>
-        </is>
-      </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>Alexandra Holmgren</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>118202633</v>
-      </c>
-      <c r="B11" t="n">
-        <v>100122</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>1332</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Nipsippa</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Pulsatilla patens</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>(L.) Mill.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>Näsåkers nipa, Ång</t>
-        </is>
-      </c>
-      <c r="Q11" t="n">
-        <v>595183</v>
-      </c>
-      <c r="R11" t="n">
-        <v>7035590</v>
-      </c>
-      <c r="S11" t="n">
-        <v>50</v>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>Sollefteå</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>Ådals-Liden</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>2024-07-03</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>2024-07-03</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>2 plantor</t>
-        </is>
-      </c>
-      <c r="AD11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF11" t="inlineStr"/>
-      <c r="AG11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT11" t="inlineStr"/>
-      <c r="AW11" t="inlineStr">
-        <is>
-          <t>Anders Malmsten</t>
-        </is>
-      </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>Anders Malmsten</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
